--- a/artfynd/A 42385-2024 artfynd.xlsx
+++ b/artfynd/A 42385-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112387613</v>
+        <v>112387605</v>
       </c>
       <c r="B2" t="n">
-        <v>89671</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503571</v>
+        <v>503510</v>
       </c>
       <c r="R2" t="n">
-        <v>7161473</v>
+        <v>7161446</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,324 +773,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>112387633</v>
-      </c>
-      <c r="B3" t="n">
-        <v>89671</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Invikne, Jmt</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>503630</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7161428</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>112387614</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89671</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Invikne, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>503649</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7161488</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>112387605</v>
-      </c>
-      <c r="B5" t="n">
-        <v>90335</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Invikne, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>503511</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7161446</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
